--- a/Pedidos_GustoBot.xlsx
+++ b/Pedidos_GustoBot.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Pedidos" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
   <si>
     <t>Fecha_Hora</t>
   </si>
@@ -79,42 +79,61 @@
     <t>3 hamburguesas dobles, 3 papas fritas grandes, 1 bebida grande</t>
   </si>
   <si>
-    <t>Mariol</t>
-  </si>
-  <si>
-    <t>mariol@gmail.net</t>
-  </si>
-  <si>
-    <t>2 chaguarmas mixtos, 2 bebidas coca cola</t>
-  </si>
-  <si>
-    <t>2026-10-18T12:00:00+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T15:30:00Z</t>
-  </si>
-  <si>
-    <t>2026-10-18T??:??:??</t>
+    <t>2026-10-24T12:00:00Z</t>
   </si>
   <si>
     <t>Marcelo</t>
   </si>
   <si>
-    <t>mache@gmaim.net</t>
-  </si>
-  <si>
-    <t>Helado x1, Hamburguesa x2, Coca Cola 1L x1</t>
-  </si>
-  <si>
-    <t>No hay notas</t>
+    <t>Comida china, opción 1</t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:45:00Z</t>
+  </si>
+  <si>
+    <t>Comida china - Opción 1</t>
+  </si>
+  <si>
+    <t>Salchipapas x1</t>
+  </si>
+  <si>
+    <t>Menú Opción 1 (Individual) x1</t>
+  </si>
+  <si>
+    <t>2026-10-25T12:34:56Z</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>FAST-002 (Papas Fritas Grandes) x1, BEB-001 (Coca-Cola Original 350ml) x1</t>
+  </si>
+  <si>
+    <t>juanin</t>
+  </si>
+  <si>
+    <t>1 x Coca-Cola Original 350ml</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:00:00-03:00</t>
+  </si>
+  <si>
+    <t>Pepito</t>
+  </si>
+  <si>
+    <t>1 Papas Fritas Grandes, 1 Coca-Cola Original 350ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -149,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -163,6 +182,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -385,7 +407,7 @@
     <col customWidth="1" min="3" max="3" width="14.75"/>
     <col customWidth="1" min="4" max="4" width="20.38"/>
     <col customWidth="1" min="5" max="5" width="10.88"/>
-    <col customWidth="1" min="6" max="6" width="35.38"/>
+    <col customWidth="1" min="6" max="6" width="52.0"/>
     <col customWidth="1" min="7" max="7" width="23.0"/>
     <col customWidth="1" min="8" max="8" width="19.63"/>
   </cols>
@@ -567,49 +589,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
-        <v>46313.52425925926</v>
+      <c r="A8" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="4">
-        <v>56745612378</v>
-      </c>
-      <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C8" s="3">
+        <v>9.12345678E8</v>
+      </c>
       <c r="E8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4">
-        <v>56912345678</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.12345678E8</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>13</v>
@@ -617,81 +630,106 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4">
-        <v>56912345678</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="C10" s="3">
+        <v>9.12345678E8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
+      <c r="A11" s="2">
+        <v>46320.52425925926</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="C11" s="3">
+        <v>9.1234677E7</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
-        <v>46313.5</v>
+      <c r="A12" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3">
-        <v>8.9900665E8</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>9.87654321E8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>46320.416666666664</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="3">
+        <v>8.91234567E8</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7.12345678E8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
